--- a/DanhSachSinhVien_(220236_06).xlsx
+++ b/DanhSachSinhVien_(220236_06).xlsx
@@ -716,10 +716,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1073,40 +1073,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="G1" s="5" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="G1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="5"/>
+      <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="G2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="G2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="5"/>
+      <c r="H2" s="6"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="7" spans="1:11">
       <c r="B7" s="1" t="s">
@@ -1178,10 +1178,10 @@
       <c r="I11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="5" t="s">
         <v>190</v>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
         <v>105</v>
       </c>
       <c r="K22">
-        <v>4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1829,7 +1829,7 @@
         <v>181</v>
       </c>
       <c r="K33">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:11">

--- a/DanhSachSinhVien_(220236_06).xlsx
+++ b/DanhSachSinhVien_(220236_06).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="192">
   <si>
     <t>Đại học Trà Vinh</t>
   </si>
@@ -592,6 +592,9 @@
   </si>
   <si>
     <t>Buổi 2</t>
+  </si>
+  <si>
+    <t>Buổi 3</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -1072,7 +1075,7 @@
     <col min="9" max="9" width="30.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1083,7 +1086,7 @@
       </c>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
@@ -1094,21 +1097,21 @@
       </c>
       <c r="H2" s="6"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="D4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="D5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1122,7 +1125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1150,7 +1153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1184,8 +1187,11 @@
       <c r="K11" s="5" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -1214,7 +1220,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:12">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
@@ -1243,7 +1249,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:12">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1272,7 +1278,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:12">
       <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
@@ -1301,7 +1307,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:12">
       <c r="A16" s="3" t="s">
         <v>56</v>
       </c>

--- a/DanhSachSinhVien_(220236_06).xlsx
+++ b/DanhSachSinhVien_(220236_06).xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\07052026\my-project-da25ttb-to-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tkw\my-project-da25ttb-to-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="193">
   <si>
     <t>Đại học Trà Vinh</t>
   </si>
@@ -595,6 +595,9 @@
   </si>
   <si>
     <t>Buổi 3</t>
+  </si>
+  <si>
+    <t>chuyển nhóm</t>
   </si>
 </sst>
 </file>
@@ -624,7 +627,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -634,6 +637,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE0E0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -705,7 +714,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -723,6 +732,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1307,36 +1323,39 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:12" s="9" customFormat="1">
+      <c r="A16" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="E16" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="3" t="s">
         <v>63</v>
       </c>
@@ -1365,7 +1384,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:12">
       <c r="A18" s="3" t="s">
         <v>70</v>
       </c>
@@ -1397,7 +1416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:12">
       <c r="A19" s="3" t="s">
         <v>77</v>
       </c>
@@ -1426,7 +1445,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:12">
       <c r="A20" s="3" t="s">
         <v>84</v>
       </c>
@@ -1455,7 +1474,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:12">
       <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
@@ -1484,7 +1503,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:12">
       <c r="A22" s="3" t="s">
         <v>100</v>
       </c>
@@ -1516,7 +1535,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:12">
       <c r="A23" s="3" t="s">
         <v>106</v>
       </c>
@@ -1545,7 +1564,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:12">
       <c r="A24" s="3" t="s">
         <v>113</v>
       </c>
@@ -1574,7 +1593,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:12">
       <c r="A25" s="3" t="s">
         <v>120</v>
       </c>
@@ -1603,7 +1622,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:12">
       <c r="A26" s="3" t="s">
         <v>127</v>
       </c>
@@ -1632,7 +1651,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:12">
       <c r="A27" s="3" t="s">
         <v>134</v>
       </c>
@@ -1661,7 +1680,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:12">
       <c r="A28" s="3" t="s">
         <v>141</v>
       </c>
@@ -1690,7 +1709,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:12">
       <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
@@ -1719,7 +1738,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:12">
       <c r="A30" s="3" t="s">
         <v>154</v>
       </c>
@@ -1747,8 +1766,11 @@
       <c r="I30" s="3" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="3" t="s">
         <v>161</v>
       </c>
@@ -1777,68 +1799,74 @@
         <v>167</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:12" s="9" customFormat="1">
+      <c r="A32" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G32" s="3" t="s">
+      <c r="E32" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="7" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="3" t="s">
+      <c r="L32" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="9" customFormat="1">
+      <c r="A33" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G33" s="3" t="s">
+      <c r="E33" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="L33" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" s="3" t="s">
         <v>182</v>
       </c>

--- a/DanhSachSinhVien_(220236_06).xlsx
+++ b/DanhSachSinhVien_(220236_06).xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="DanhSachSV" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="195">
   <si>
     <t>Đại học Trà Vinh</t>
   </si>
@@ -598,6 +598,12 @@
   </si>
   <si>
     <t>chuyển nhóm</t>
+  </si>
+  <si>
+    <t>Buổi 4</t>
+  </si>
+  <si>
+    <t>Chuyển nhóm sáng</t>
   </si>
 </sst>
 </file>
@@ -646,7 +652,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -701,20 +707,37 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="thin">
         <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -728,9 +751,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -739,6 +759,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1078,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -1091,43 +1126,43 @@
     <col min="9" max="9" width="30.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="G1" s="6" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="G1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="6"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="6" t="s">
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="G2" s="6" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="G2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="D4" s="6" t="s">
+      <c r="H2" s="9"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="D4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="D5" s="6" t="s">
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="D5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1141,7 +1176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1155,7 +1190,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1169,7 +1204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1194,20 +1229,23 @@
       <c r="H11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="L11" s="13" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -1232,11 +1270,17 @@
       <c r="H12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
@@ -1261,11 +1305,15 @@
       <c r="H13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="11" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1290,11 +1338,15 @@
       <c r="H14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="11" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
@@ -1319,43 +1371,52 @@
       <c r="H15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="11" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" s="9" customFormat="1">
-      <c r="A16" s="7" t="s">
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+    </row>
+    <row r="16" spans="1:13" s="8" customFormat="1">
+      <c r="A16" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3" t="s">
         <v>63</v>
       </c>
@@ -1380,11 +1441,15 @@
       <c r="H17" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="11" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3" t="s">
         <v>70</v>
       </c>
@@ -1409,14 +1474,17 @@
       <c r="H18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="3" t="s">
         <v>77</v>
       </c>
@@ -1441,11 +1509,15 @@
       <c r="H19" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="11" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="3" t="s">
         <v>84</v>
       </c>
@@ -1470,11 +1542,15 @@
       <c r="H20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="11" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
@@ -1499,11 +1575,15 @@
       <c r="H21" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="11" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="3" t="s">
         <v>100</v>
       </c>
@@ -1528,14 +1608,17 @@
       <c r="H22" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="K22">
+      <c r="J22" s="14"/>
+      <c r="K22" s="14">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="3" t="s">
         <v>106</v>
       </c>
@@ -1560,11 +1643,15 @@
       <c r="H23" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="11" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="3" t="s">
         <v>113</v>
       </c>
@@ -1589,11 +1676,15 @@
       <c r="H24" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="11" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="3" t="s">
         <v>120</v>
       </c>
@@ -1618,11 +1709,15 @@
       <c r="H25" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="3" t="s">
         <v>127</v>
       </c>
@@ -1647,11 +1742,15 @@
       <c r="H26" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="11" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="3" t="s">
         <v>134</v>
       </c>
@@ -1676,11 +1775,15 @@
       <c r="H27" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="11" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="3" t="s">
         <v>141</v>
       </c>
@@ -1705,11 +1808,15 @@
       <c r="H28" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="11" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
@@ -1734,43 +1841,50 @@
       <c r="H29" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="11" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="3" t="s">
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+    </row>
+    <row r="30" spans="1:13" s="8" customFormat="1">
+      <c r="A30" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H30" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="L30">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="M30" s="15"/>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="3" t="s">
         <v>161</v>
       </c>
@@ -1795,78 +1909,91 @@
       <c r="H31" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="11" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" s="9" customFormat="1">
-      <c r="A32" s="7" t="s">
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+    </row>
+    <row r="32" spans="1:13" s="8" customFormat="1">
+      <c r="A32" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I32" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" s="9" customFormat="1">
-      <c r="A33" s="7" t="s">
+      <c r="M32" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="8" customFormat="1">
+      <c r="A33" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H33" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="I33" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="K33" s="9">
+      <c r="J33" s="15"/>
+      <c r="K33" s="15">
         <v>2</v>
       </c>
-      <c r="L33" s="9" t="s">
+      <c r="L33" s="15" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="M33" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="3" t="s">
         <v>182</v>
       </c>
@@ -1891,8 +2018,30 @@
       <c r="H34" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="11" t="s">
         <v>188</v>
+      </c>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="J35">
+        <f>COUNTIF(J12:J34,"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="K35" s="5">
+        <f>COUNTIF(K12:K34,"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="L35" s="5">
+        <f t="shared" ref="K35:M35" si="0">COUNTIF(L12:L34,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/DanhSachSinhVien_(220236_06).xlsx
+++ b/DanhSachSinhVien_(220236_06).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="196">
   <si>
     <t>Đại học Trà Vinh</t>
   </si>
@@ -604,6 +604,9 @@
   </si>
   <si>
     <t>Chuyển nhóm sáng</t>
+  </si>
+  <si>
+    <t>Buổi 5</t>
   </si>
 </sst>
 </file>
@@ -652,7 +655,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -733,11 +736,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -759,7 +771,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -774,6 +785,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1113,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -1124,45 +1139,46 @@
     <col min="6" max="6" width="50.85546875" customWidth="1"/>
     <col min="7" max="8" width="15.85546875" customWidth="1"/>
     <col min="9" max="9" width="30.85546875" customWidth="1"/>
+    <col min="10" max="13" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="G1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="9"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="9" t="s">
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="G2" s="9" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="G2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="9"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="D4" s="9" t="s">
+      <c r="H2" s="15"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="D4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="D5" s="9" t="s">
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="D5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+    </row>
+    <row r="7" spans="1:14">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1176,7 +1192,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1190,7 +1206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1204,7 +1220,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1229,23 +1245,26 @@
       <c r="H11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="12" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11" s="16" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -1270,17 +1289,17 @@
       <c r="H12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14">
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:14">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
@@ -1305,15 +1324,15 @@
       <c r="H13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1338,15 +1357,15 @@
       <c r="H14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
@@ -1371,15 +1390,15 @@
       <c r="H15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-    </row>
-    <row r="16" spans="1:13" s="8" customFormat="1">
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" spans="1:14" s="8" customFormat="1">
       <c r="A16" s="6" t="s">
         <v>56</v>
       </c>
@@ -1404,19 +1423,19 @@
       <c r="H16" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15" t="s">
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="M16" s="15">
+      <c r="M16" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:14">
       <c r="A17" s="3" t="s">
         <v>63</v>
       </c>
@@ -1441,15 +1460,15 @@
       <c r="H17" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3" t="s">
         <v>70</v>
       </c>
@@ -1474,17 +1493,17 @@
       <c r="H18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>4</v>
       </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3" t="s">
         <v>77</v>
       </c>
@@ -1509,15 +1528,15 @@
       <c r="H19" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3" t="s">
         <v>84</v>
       </c>
@@ -1542,15 +1561,15 @@
       <c r="H20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
@@ -1575,15 +1594,15 @@
       <c r="H21" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3" t="s">
         <v>100</v>
       </c>
@@ -1608,17 +1627,17 @@
       <c r="H22" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14">
+      <c r="J22" s="13"/>
+      <c r="K22" s="13">
         <v>1.5</v>
       </c>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3" t="s">
         <v>106</v>
       </c>
@@ -1643,15 +1662,15 @@
       <c r="H23" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="3" t="s">
         <v>113</v>
       </c>
@@ -1676,15 +1695,15 @@
       <c r="H24" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="3" t="s">
         <v>120</v>
       </c>
@@ -1709,15 +1728,15 @@
       <c r="H25" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="3" t="s">
         <v>127</v>
       </c>
@@ -1742,15 +1761,18 @@
       <c r="H26" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="3" t="s">
         <v>134</v>
       </c>
@@ -1775,15 +1797,15 @@
       <c r="H27" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="3" t="s">
         <v>141</v>
       </c>
@@ -1808,15 +1830,15 @@
       <c r="H28" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
@@ -1841,15 +1863,15 @@
       <c r="H29" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-    </row>
-    <row r="30" spans="1:13" s="8" customFormat="1">
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+    </row>
+    <row r="30" spans="1:14" s="8" customFormat="1">
       <c r="A30" s="6" t="s">
         <v>154</v>
       </c>
@@ -1874,17 +1896,17 @@
       <c r="H30" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="I30" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15" t="s">
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="M30" s="15"/>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="M30" s="14"/>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="3" t="s">
         <v>161</v>
       </c>
@@ -1909,15 +1931,15 @@
       <c r="H31" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-    </row>
-    <row r="32" spans="1:13" s="8" customFormat="1">
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+    </row>
+    <row r="32" spans="1:14" s="8" customFormat="1">
       <c r="A32" s="6" t="s">
         <v>168</v>
       </c>
@@ -1942,15 +1964,15 @@
       <c r="H32" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15" t="s">
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="M32" s="15">
+      <c r="M32" s="14">
         <v>4</v>
       </c>
     </row>
@@ -1979,17 +2001,17 @@
       <c r="H33" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="I33" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15">
+      <c r="J33" s="14"/>
+      <c r="K33" s="14">
         <v>2</v>
       </c>
-      <c r="L33" s="15" t="s">
+      <c r="L33" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="M33" s="15">
+      <c r="M33" s="14">
         <v>4</v>
       </c>
     </row>
@@ -2018,13 +2040,13 @@
       <c r="H34" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
     </row>
     <row r="35" spans="1:13">
       <c r="J35">
@@ -2036,7 +2058,7 @@
         <v>2</v>
       </c>
       <c r="L35" s="5">
-        <f t="shared" ref="K35:M35" si="0">COUNTIF(L12:L34,"&gt;0")</f>
+        <f t="shared" ref="L35:M35" si="0">COUNTIF(L12:L34,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M35" s="5">

--- a/DanhSachSinhVien_(220236_06).xlsx
+++ b/DanhSachSinhVien_(220236_06).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="197">
   <si>
     <t>Đại học Trà Vinh</t>
   </si>
@@ -607,6 +607,9 @@
   </si>
   <si>
     <t>Buổi 5</t>
+  </si>
+  <si>
+    <t>Buổi 6</t>
   </si>
 </sst>
 </file>
@@ -749,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -789,6 +792,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1128,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -1142,43 +1146,43 @@
     <col min="10" max="13" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="G1" s="15" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="G1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="15"/>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="15" t="s">
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="G2" s="15" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="D4" s="15" t="s">
+      <c r="H2" s="17"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="D4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="D5" s="15" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="D5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="7" spans="1:15">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1192,7 +1196,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1206,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1220,7 +1224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1263,8 +1267,11 @@
       <c r="N11" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" s="16" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -1299,7 +1306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
@@ -1332,7 +1339,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1365,7 +1372,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="13"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
@@ -1398,7 +1405,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
     </row>
-    <row r="16" spans="1:14" s="8" customFormat="1">
+    <row r="16" spans="1:15" s="8" customFormat="1">
       <c r="A16" s="6" t="s">
         <v>56</v>
       </c>
@@ -1435,7 +1442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:15">
       <c r="A17" s="3" t="s">
         <v>63</v>
       </c>
@@ -1468,7 +1475,7 @@
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:15">
       <c r="A18" s="3" t="s">
         <v>70</v>
       </c>
@@ -1502,8 +1509,11 @@
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="3" t="s">
         <v>77</v>
       </c>
@@ -1536,7 +1546,7 @@
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:15">
       <c r="A20" s="3" t="s">
         <v>84</v>
       </c>
@@ -1569,7 +1579,7 @@
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:15">
       <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
@@ -1602,7 +1612,7 @@
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:15">
       <c r="A22" s="3" t="s">
         <v>100</v>
       </c>
@@ -1637,7 +1647,7 @@
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:15">
       <c r="A23" s="3" t="s">
         <v>106</v>
       </c>
@@ -1670,7 +1680,7 @@
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:15">
       <c r="A24" s="3" t="s">
         <v>113</v>
       </c>
@@ -1703,7 +1713,7 @@
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:15">
       <c r="A25" s="3" t="s">
         <v>120</v>
       </c>
@@ -1736,7 +1746,7 @@
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:15">
       <c r="A26" s="3" t="s">
         <v>127</v>
       </c>
@@ -1772,7 +1782,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:15">
       <c r="A27" s="3" t="s">
         <v>134</v>
       </c>
@@ -1805,7 +1815,7 @@
       <c r="L27" s="13"/>
       <c r="M27" s="13"/>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:15">
       <c r="A28" s="3" t="s">
         <v>141</v>
       </c>
@@ -1838,7 +1848,7 @@
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:15">
       <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
@@ -1871,7 +1881,7 @@
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
     </row>
-    <row r="30" spans="1:14" s="8" customFormat="1">
+    <row r="30" spans="1:15" s="8" customFormat="1">
       <c r="A30" s="6" t="s">
         <v>154</v>
       </c>
@@ -1906,7 +1916,7 @@
       </c>
       <c r="M30" s="14"/>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:15">
       <c r="A31" s="3" t="s">
         <v>161</v>
       </c>
@@ -1939,7 +1949,7 @@
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
     </row>
-    <row r="32" spans="1:14" s="8" customFormat="1">
+    <row r="32" spans="1:15" s="8" customFormat="1">
       <c r="A32" s="6" t="s">
         <v>168</v>
       </c>
@@ -1976,7 +1986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:13" s="8" customFormat="1">
+    <row r="33" spans="1:15" s="8" customFormat="1">
       <c r="A33" s="6" t="s">
         <v>175</v>
       </c>
@@ -2015,7 +2025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:15">
       <c r="A34" s="3" t="s">
         <v>182</v>
       </c>
@@ -2048,7 +2058,7 @@
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:15">
       <c r="J35">
         <f>COUNTIF(J12:J34,"&gt;0")</f>
         <v>1</v>
@@ -2058,12 +2068,20 @@
         <v>2</v>
       </c>
       <c r="L35" s="5">
-        <f t="shared" ref="L35:M35" si="0">COUNTIF(L12:L34,"&gt;0")</f>
+        <f t="shared" ref="L35:O35" si="0">COUNTIF(L12:L34,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M35" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
+      </c>
+      <c r="N35" s="15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O35" s="15">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DanhSachSinhVien_(220236_06).xlsx
+++ b/DanhSachSinhVien_(220236_06).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="198">
   <si>
     <t>Đại học Trà Vinh</t>
   </si>
@@ -610,6 +610,9 @@
   </si>
   <si>
     <t>Buổi 6</t>
+  </si>
+  <si>
+    <t>Buổi 7</t>
   </si>
 </sst>
 </file>
@@ -752,7 +755,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -792,6 +795,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1132,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -1146,43 +1150,43 @@
     <col min="10" max="13" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="G1" s="17" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="G1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="17" t="s">
+      <c r="H1" s="18"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="G2" s="17" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="G2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="17"/>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="D4" s="17" t="s">
+      <c r="H2" s="18"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="D4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="D5" s="17" t="s">
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="D5" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+    </row>
+    <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1196,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1210,7 +1214,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1224,7 +1228,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1270,8 +1274,11 @@
       <c r="O11" s="16" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="P11" s="16" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -1306,7 +1313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
@@ -1339,7 +1346,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1372,7 +1379,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="13"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:16">
       <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
@@ -1405,7 +1412,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
     </row>
-    <row r="16" spans="1:15" s="8" customFormat="1">
+    <row r="16" spans="1:16" s="8" customFormat="1">
       <c r="A16" s="6" t="s">
         <v>56</v>
       </c>
@@ -1442,7 +1449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:16">
       <c r="A17" s="3" t="s">
         <v>63</v>
       </c>
@@ -1475,7 +1482,7 @@
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:16">
       <c r="A18" s="3" t="s">
         <v>70</v>
       </c>
@@ -1513,7 +1520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:16">
       <c r="A19" s="3" t="s">
         <v>77</v>
       </c>
@@ -1546,7 +1553,7 @@
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:16">
       <c r="A20" s="3" t="s">
         <v>84</v>
       </c>
@@ -1579,7 +1586,7 @@
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:16">
       <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
@@ -1612,7 +1619,7 @@
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:16">
       <c r="A22" s="3" t="s">
         <v>100</v>
       </c>
@@ -1647,7 +1654,7 @@
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:16">
       <c r="A23" s="3" t="s">
         <v>106</v>
       </c>
@@ -1680,7 +1687,7 @@
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:16">
       <c r="A24" s="3" t="s">
         <v>113</v>
       </c>
@@ -1712,8 +1719,11 @@
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="P24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="3" t="s">
         <v>120</v>
       </c>
@@ -1746,7 +1756,7 @@
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:16">
       <c r="A26" s="3" t="s">
         <v>127</v>
       </c>
@@ -1781,8 +1791,11 @@
       <c r="N26">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="P26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="3" t="s">
         <v>134</v>
       </c>
@@ -1815,7 +1828,7 @@
       <c r="L27" s="13"/>
       <c r="M27" s="13"/>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:16">
       <c r="A28" s="3" t="s">
         <v>141</v>
       </c>
@@ -1848,7 +1861,7 @@
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:16">
       <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
@@ -1881,7 +1894,7 @@
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
     </row>
-    <row r="30" spans="1:15" s="8" customFormat="1">
+    <row r="30" spans="1:16" s="8" customFormat="1">
       <c r="A30" s="6" t="s">
         <v>154</v>
       </c>
@@ -1916,7 +1929,7 @@
       </c>
       <c r="M30" s="14"/>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:16">
       <c r="A31" s="3" t="s">
         <v>161</v>
       </c>
@@ -1949,7 +1962,7 @@
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
     </row>
-    <row r="32" spans="1:15" s="8" customFormat="1">
+    <row r="32" spans="1:16" s="8" customFormat="1">
       <c r="A32" s="6" t="s">
         <v>168</v>
       </c>
@@ -1986,7 +1999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="8" customFormat="1">
+    <row r="33" spans="1:16" s="8" customFormat="1">
       <c r="A33" s="6" t="s">
         <v>175</v>
       </c>
@@ -2025,7 +2038,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:16">
       <c r="A34" s="3" t="s">
         <v>182</v>
       </c>
@@ -2058,7 +2071,7 @@
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:16">
       <c r="J35">
         <f>COUNTIF(J12:J34,"&gt;0")</f>
         <v>1</v>
@@ -2068,7 +2081,7 @@
         <v>2</v>
       </c>
       <c r="L35" s="5">
-        <f t="shared" ref="L35:O35" si="0">COUNTIF(L12:L34,"&gt;0")</f>
+        <f t="shared" ref="L35:P35" si="0">COUNTIF(L12:L34,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M35" s="5">
@@ -2082,6 +2095,10 @@
       <c r="O35" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
+      </c>
+      <c r="P35" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/DanhSachSinhVien_(220236_06).xlsx
+++ b/DanhSachSinhVien_(220236_06).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="199">
   <si>
     <t>Đại học Trà Vinh</t>
   </si>
@@ -613,6 +613,9 @@
   </si>
   <si>
     <t>Buổi 7</t>
+  </si>
+  <si>
+    <t>Buổi 8</t>
   </si>
 </sst>
 </file>
@@ -755,7 +758,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -795,6 +798,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -1136,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -1150,43 +1155,43 @@
     <col min="10" max="13" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="G1" s="18" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="G1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="18"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="18" t="s">
+      <c r="H1" s="20"/>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="G2" s="18" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="G2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="18"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="D4" s="18" t="s">
+      <c r="H2" s="20"/>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="D4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="D5" s="18" t="s">
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="D5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+    </row>
+    <row r="7" spans="1:18">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1200,7 +1205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:18">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1214,7 +1219,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:18">
       <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1228,7 +1233,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1277,8 +1282,11 @@
       <c r="P11" s="16" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="16" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -1312,8 +1320,11 @@
       <c r="M12" s="13">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="R12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
@@ -1345,8 +1356,11 @@
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="R13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1378,8 +1392,14 @@
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
       <c r="M14" s="13"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14">
+        <v>4</v>
+      </c>
+      <c r="R14" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
@@ -1411,8 +1431,11 @@
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
-    </row>
-    <row r="16" spans="1:16" s="8" customFormat="1">
+      <c r="R15" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="8" customFormat="1">
       <c r="A16" s="6" t="s">
         <v>56</v>
       </c>
@@ -1448,8 +1471,11 @@
       <c r="M16" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="R16" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="3" t="s">
         <v>63</v>
       </c>
@@ -1481,8 +1507,11 @@
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="R17" s="19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="3" t="s">
         <v>70</v>
       </c>
@@ -1519,8 +1548,11 @@
       <c r="O18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="R18" s="19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="3" t="s">
         <v>77</v>
       </c>
@@ -1552,8 +1584,11 @@
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="R19" s="19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="3" t="s">
         <v>84</v>
       </c>
@@ -1585,8 +1620,11 @@
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="R20" s="19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
@@ -1618,8 +1656,11 @@
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="R21" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="3" t="s">
         <v>100</v>
       </c>
@@ -1653,8 +1694,11 @@
       </c>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="R22" s="19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" s="3" t="s">
         <v>106</v>
       </c>
@@ -1686,8 +1730,11 @@
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="R23" s="19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" s="3" t="s">
         <v>113</v>
       </c>
@@ -1720,10 +1767,13 @@
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="P24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
+        <v>2</v>
+      </c>
+      <c r="R24" s="19">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="3" t="s">
         <v>120</v>
       </c>
@@ -1755,8 +1805,11 @@
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="R25" s="19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" s="3" t="s">
         <v>127</v>
       </c>
@@ -1792,10 +1845,13 @@
         <v>4</v>
       </c>
       <c r="P26">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+        <v>2</v>
+      </c>
+      <c r="R26" s="19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" s="3" t="s">
         <v>134</v>
       </c>
@@ -1827,8 +1883,11 @@
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
       <c r="M27" s="13"/>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="R27" s="19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="3" t="s">
         <v>141</v>
       </c>
@@ -1860,8 +1919,11 @@
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="R28" s="19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
@@ -1893,8 +1955,11 @@
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
-    </row>
-    <row r="30" spans="1:16" s="8" customFormat="1">
+      <c r="R29" s="19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="8" customFormat="1">
       <c r="A30" s="6" t="s">
         <v>154</v>
       </c>
@@ -1928,8 +1993,11 @@
         <v>194</v>
       </c>
       <c r="M30" s="14"/>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="R30" s="19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" s="3" t="s">
         <v>161</v>
       </c>
@@ -1961,8 +2029,11 @@
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
-    </row>
-    <row r="32" spans="1:16" s="8" customFormat="1">
+      <c r="R31" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" s="8" customFormat="1">
       <c r="A32" s="6" t="s">
         <v>168</v>
       </c>
@@ -1998,8 +2069,11 @@
       <c r="M32" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" s="8" customFormat="1">
+      <c r="R32" s="19">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" s="8" customFormat="1">
       <c r="A33" s="6" t="s">
         <v>175</v>
       </c>
@@ -2037,8 +2111,11 @@
       <c r="M33" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:16">
+      <c r="R33" s="19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" s="3" t="s">
         <v>182</v>
       </c>
@@ -2070,8 +2147,11 @@
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="R34" s="19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
       <c r="J35">
         <f>COUNTIF(J12:J34,"&gt;0")</f>
         <v>1</v>
@@ -2081,7 +2161,7 @@
         <v>2</v>
       </c>
       <c r="L35" s="5">
-        <f t="shared" ref="L35:P35" si="0">COUNTIF(L12:L34,"&gt;0")</f>
+        <f t="shared" ref="L35:Q35" si="0">COUNTIF(L12:L34,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M35" s="5">
@@ -2099,6 +2179,10 @@
       <c r="P35" s="17">
         <f t="shared" si="0"/>
         <v>2</v>
+      </c>
+      <c r="Q35" s="18">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
